--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53011-2024 artfynd.xlsx
+++ b/artfynd/A 53011-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153374</v>
       </c>
       <c r="B2" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
